--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$36</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/PractitionerRole</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-practitionerrole</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -1007,6 +1010,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1346,7 +1364,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1458,7 +1476,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1572,7 +1590,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1684,7 +1702,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -1798,7 +1816,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -1912,7 +1930,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2026,7 +2044,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2140,7 +2158,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2254,7 +2272,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2370,7 +2388,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2484,7 +2502,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
@@ -2602,7 +2620,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>164</v>
       </c>
@@ -2716,7 +2734,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>173</v>
       </c>
@@ -2735,7 +2753,7 @@
         <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>77</v>
@@ -2828,7 +2846,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>178</v>
       </c>
@@ -2940,7 +2958,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>183</v>
       </c>
@@ -3056,7 +3074,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>194</v>
       </c>
@@ -3168,7 +3186,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>202</v>
       </c>
@@ -3280,7 +3298,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>209</v>
       </c>
@@ -3392,7 +3410,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>215</v>
       </c>
@@ -3506,7 +3524,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>221</v>
       </c>
@@ -3620,7 +3638,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>227</v>
       </c>
@@ -3732,7 +3750,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>233</v>
       </c>
@@ -3846,7 +3864,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>236</v>
       </c>
@@ -3962,7 +3980,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>241</v>
       </c>
@@ -4074,7 +4092,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>247</v>
       </c>
@@ -4186,7 +4204,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>250</v>
       </c>
@@ -4300,7 +4318,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>255</v>
       </c>
@@ -4414,7 +4432,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>258</v>
       </c>
@@ -4526,7 +4544,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>261</v>
       </c>
@@ -4638,7 +4656,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>262</v>
       </c>
@@ -4752,7 +4770,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>263</v>
       </c>
@@ -4868,7 +4886,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>264</v>
       </c>
@@ -4980,7 +4998,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>267</v>
       </c>
@@ -5092,7 +5110,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>270</v>
       </c>
@@ -5204,7 +5222,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>273</v>
       </c>
@@ -5319,6 +5337,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN36">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI35">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner-role.xlsx
+++ b/StructureDefinition-dk-core-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
